--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/feb-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>584.97</v>
+        <v>26957.34</v>
       </c>
     </row>
     <row r="3">
@@ -630,11 +630,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12119.4</v>
+        <v>558501.78</v>
       </c>
     </row>
     <row r="4">
@@ -691,11 +691,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1697.5</v>
+        <v>78226.38</v>
       </c>
     </row>
     <row r="5">
@@ -756,11 +756,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9227.8441</v>
+        <v>425249.38</v>
       </c>
     </row>
     <row r="6">
@@ -821,11 +821,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>161.51989</v>
+        <v>7443.37</v>
       </c>
     </row>
     <row r="7">
@@ -882,11 +882,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5499.9992</v>
+        <v>253458.04</v>
       </c>
     </row>
     <row r="8">
@@ -943,11 +943,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>490.8447</v>
+        <v>22619.74</v>
       </c>
     </row>
     <row r="9">
@@ -1004,11 +1004,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>399.9</v>
+        <v>18428.71</v>
       </c>
     </row>
     <row r="10">
@@ -1065,11 +1065,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>549.8596</v>
+        <v>25339.34</v>
       </c>
     </row>
     <row r="11">
@@ -1126,11 +1126,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>433.008</v>
+        <v>19954.43</v>
       </c>
     </row>
     <row r="12">
@@ -1187,11 +1187,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>428.7858</v>
+        <v>19759.86</v>
       </c>
     </row>
     <row r="13">
@@ -1248,11 +1248,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>235.29</v>
+        <v>10842.94</v>
       </c>
     </row>
     <row r="14">
@@ -1309,11 +1309,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1012</v>
+        <v>46636.29</v>
       </c>
     </row>
     <row r="15">
@@ -1370,11 +1370,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>742.5599999999999</v>
+        <v>34219.61</v>
       </c>
     </row>
     <row r="16">
@@ -1431,11 +1431,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9270</v>
+        <v>427192.07</v>
       </c>
     </row>
     <row r="17">
@@ -1492,11 +1492,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1364.3112</v>
+        <v>62871.94</v>
       </c>
     </row>
     <row r="18">
@@ -1553,11 +1553,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>184.3</v>
+        <v>8493.15</v>
       </c>
     </row>
     <row r="19">
@@ -1614,11 +1614,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1613.68</v>
+        <v>74363.67999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4832.2456</v>
+        <v>222685.76</v>
       </c>
     </row>
     <row r="21">
@@ -1740,11 +1740,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>179.928</v>
+        <v>8291.67</v>
       </c>
     </row>
     <row r="22">
@@ -1801,11 +1801,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>880.3200000000001</v>
+        <v>40568.04</v>
       </c>
     </row>
     <row r="23">
@@ -1862,11 +1862,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>698.4</v>
+        <v>32184.57</v>
       </c>
     </row>
     <row r="24">
@@ -1923,11 +1923,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>920</v>
+        <v>42396.62</v>
       </c>
     </row>
     <row r="25">
@@ -1984,11 +1984,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>163.6649</v>
+        <v>7542.22</v>
       </c>
     </row>
     <row r="26">
@@ -2045,11 +2045,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1060.21</v>
+        <v>48857.96</v>
       </c>
     </row>
     <row r="27">
@@ -2106,11 +2106,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>380.919</v>
+        <v>17554</v>
       </c>
     </row>
     <row r="28">
@@ -2167,11 +2167,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1569.8</v>
+        <v>72341.53999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2228,11 +2228,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2432.2569</v>
+        <v>112086.39</v>
       </c>
     </row>
     <row r="30">
@@ -2289,11 +2289,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1571.36</v>
+        <v>72413.42999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2350,11 +2350,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>339.7569</v>
+        <v>15657.11</v>
       </c>
     </row>
     <row r="32">
@@ -2411,11 +2411,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1105.748</v>
+        <v>50956.5</v>
       </c>
     </row>
     <row r="33">
@@ -2476,11 +2476,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>172.33</v>
+        <v>7941.53</v>
       </c>
     </row>
     <row r="34">
@@ -2537,11 +2537,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>604.1105</v>
+        <v>27839.4</v>
       </c>
     </row>
     <row r="35">
@@ -2598,11 +2598,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>994.25</v>
+        <v>45818.31</v>
       </c>
     </row>
     <row r="36">
@@ -2659,11 +2659,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>947.52</v>
+        <v>43664.84</v>
       </c>
     </row>
     <row r="37">
@@ -2720,11 +2720,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1298.0556</v>
+        <v>59818.67</v>
       </c>
     </row>
     <row r="38">
@@ -2781,11 +2781,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1232.87</v>
+        <v>56814.7</v>
       </c>
     </row>
     <row r="39">
@@ -2842,11 +2842,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1653.936</v>
+        <v>76218.81</v>
       </c>
     </row>
     <row r="40">
@@ -2903,11 +2903,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1681.5671</v>
+        <v>77492.14</v>
       </c>
     </row>
     <row r="41">
@@ -2964,11 +2964,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>427.8</v>
+        <v>19714.43</v>
       </c>
     </row>
     <row r="42">
@@ -3025,11 +3025,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>821.4930000000001</v>
+        <v>37857.1</v>
       </c>
     </row>
     <row r="43">
@@ -3086,11 +3086,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>252.2</v>
+        <v>11622.2</v>
       </c>
     </row>
     <row r="44">
@@ -3147,11 +3147,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>572.85</v>
+        <v>26398.81</v>
       </c>
     </row>
     <row r="45">
@@ -3208,11 +3208,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>355.2237</v>
+        <v>16369.88</v>
       </c>
     </row>
     <row r="46">
@@ -3269,11 +3269,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>651.7</v>
+        <v>30032.48</v>
       </c>
     </row>
     <row r="47">
@@ -3330,11 +3330,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1435.6</v>
+        <v>66157.17</v>
       </c>
     </row>
     <row r="48">
@@ -3391,11 +3391,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>299.88</v>
+        <v>13819.46</v>
       </c>
     </row>
     <row r="49">
@@ -3452,11 +3452,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>204.6</v>
+        <v>9428.639999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3513,11 +3513,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>561.63</v>
+        <v>25881.76</v>
       </c>
     </row>
     <row r="51">
@@ -3574,11 +3574,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>230.86</v>
+        <v>10638.79</v>
       </c>
     </row>
     <row r="52">
@@ -3635,11 +3635,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>436.17</v>
+        <v>20100.15</v>
       </c>
     </row>
     <row r="53">
@@ -3696,11 +3696,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9330.299999999999</v>
+        <v>429970.89</v>
       </c>
     </row>
     <row r="54">
@@ -3757,11 +3757,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1748</v>
+        <v>80553.58</v>
       </c>
     </row>
     <row r="55">
@@ -3818,11 +3818,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>361.228</v>
+        <v>16646.57</v>
       </c>
     </row>
   </sheetData>
